--- a/outputs/53161.xlsx
+++ b/outputs/53161.xlsx
@@ -1796,109 +1796,106 @@
         <v>2</v>
       </c>
       <c r="F22" s="39" t="n">
-        <f aca="false">SUMPRODUCT((F$13:F$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(F$13:F$18=1))</f>
         <v>1</v>
       </c>
       <c r="G22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((G$13:G$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(G$13:G$18=1))</f>
         <v>1</v>
       </c>
       <c r="H22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((H$13:H$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(H$13:H$18=1))</f>
         <v>1</v>
       </c>
       <c r="I22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((I$13:I$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(I$13:I$18=1))</f>
         <v>1</v>
       </c>
       <c r="J22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((J$13:J$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(J$13:J$18=1))</f>
         <v>1</v>
       </c>
       <c r="K22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((K$13:K$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(K$13:K$18=1))</f>
         <v>1</v>
       </c>
       <c r="L22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((L$13:L$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(L$13:L$18=1))</f>
         <v>1</v>
       </c>
       <c r="M22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((M$13:M$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(M$13:M$18=1))</f>
         <v>1</v>
       </c>
       <c r="N22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((N$13:N$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(N$13:N$18=1))</f>
         <v>1</v>
       </c>
       <c r="O22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((O$13:O$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(O$13:O$18=1))</f>
         <v>1</v>
       </c>
       <c r="P22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((P$13:P$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(P$13:P$18=1))</f>
         <v>1</v>
       </c>
       <c r="Q22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((Q$13:Q$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(Q$13:Q$18=1))</f>
         <v>1</v>
       </c>
       <c r="R22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((R$13:R$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(R$13:R$18=1))</f>
         <v>1</v>
       </c>
       <c r="S22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((S$13:S$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(S$13:S$18=1))</f>
         <v>1</v>
       </c>
       <c r="T22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((T$13:T$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(T$13:T$18=1))</f>
         <v>1</v>
       </c>
       <c r="U22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((U$13:U$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(U$13:U$18=1))</f>
         <v>1</v>
       </c>
       <c r="V22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((V$13:V$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(V$13:V$18=1))</f>
         <v>1</v>
       </c>
       <c r="W22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((W$13:W$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(W$13:W$18=1))</f>
         <v>1</v>
       </c>
       <c r="X22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((X$13:X$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(X$13:X$18=1))</f>
         <v>1</v>
       </c>
       <c r="Y22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((Y$13:Y$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(Y$13:Y$18=1))</f>
         <v>0</v>
       </c>
       <c r="Z22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((Z$13:Z$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(Z$13:Z$18=1))</f>
         <v>0</v>
       </c>
       <c r="AA22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((AA$13:AA$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(AA$13:AA$18=1))</f>
         <v>0</v>
       </c>
       <c r="AB22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((AB$13:AB$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(AB$13:AB$18=1))</f>
         <v>0</v>
       </c>
       <c r="AC22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((AC$13:AC$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(AC$13:AC$18=1))</f>
         <v>0</v>
       </c>
       <c r="AD22" s="27" t="n">
-        <f aca="false">SUMPRODUCT((AD$13:AD$18=1)*($F$4:$F$9))</f>
+        <f aca="false">SUMPRODUCT((F$4:F$9=1)*(AD$13:AD$18=1))</f>
         <v>0</v>
       </c>
-      <c r="AE22" s="28" t="n">
-        <f aca="false">SUMPRODUCT((AE$13:AE$18=1)*($F$4:$F$9))</f>
-        <v>0</v>
-      </c>
+      <c r="AE22" s="28"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="40" t="s">
@@ -1910,109 +1907,106 @@
         <v>3</v>
       </c>
       <c r="F23" s="42" t="n">
-        <f aca="false">SUMPRODUCT((F$13:F$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(F$13:F$18=1))</f>
         <v>1</v>
       </c>
       <c r="G23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((G$13:G$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(G$13:G$18=1))</f>
         <v>1</v>
       </c>
       <c r="H23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((H$13:H$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(H$13:H$18=1))</f>
         <v>2</v>
       </c>
       <c r="I23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((I$13:I$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(I$13:I$18=1))</f>
         <v>2</v>
       </c>
       <c r="J23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((J$13:J$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(J$13:J$18=1))</f>
         <v>3</v>
       </c>
       <c r="K23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((K$13:K$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(K$13:K$18=1))</f>
         <v>3</v>
       </c>
       <c r="L23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((L$13:L$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(L$13:L$18=1))</f>
         <v>4</v>
       </c>
       <c r="M23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((M$13:M$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(M$13:M$18=1))</f>
         <v>6</v>
       </c>
       <c r="N23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((N$13:N$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(N$13:N$18=1))</f>
         <v>6</v>
       </c>
       <c r="O23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((O$13:O$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(O$13:O$18=1))</f>
         <v>6</v>
       </c>
       <c r="P23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((P$13:P$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(P$13:P$18=1))</f>
         <v>6</v>
       </c>
       <c r="Q23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Q$13:Q$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(Q$13:Q$18=1))</f>
         <v>6</v>
       </c>
       <c r="R23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((R$13:R$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(R$13:R$18=1))</f>
         <v>6</v>
       </c>
       <c r="S23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((S$13:S$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(S$13:S$18=1))</f>
         <v>6</v>
       </c>
       <c r="T23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((T$13:T$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(T$13:T$18=1))</f>
         <v>6</v>
       </c>
       <c r="U23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((U$13:U$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(U$13:U$18=1))</f>
         <v>6</v>
       </c>
       <c r="V23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((V$13:V$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(V$13:V$18=1))</f>
         <v>6</v>
       </c>
       <c r="W23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((W$13:W$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(W$13:W$18=1))</f>
         <v>6</v>
       </c>
       <c r="X23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((X$13:X$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(X$13:X$18=1))</f>
         <v>6</v>
       </c>
       <c r="Y23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Y$13:Y$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(Y$13:Y$18=1))</f>
         <v>5</v>
       </c>
       <c r="Z23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Z$13:Z$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(Z$13:Z$18=1))</f>
         <v>5</v>
       </c>
       <c r="AA23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AA$13:AA$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(AA$13:AA$18=1))</f>
         <v>4</v>
       </c>
       <c r="AB23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AB$13:AB$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(AB$13:AB$18=1))</f>
         <v>4</v>
       </c>
       <c r="AC23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AC$13:AC$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(AC$13:AC$18=1))</f>
         <v>3</v>
       </c>
       <c r="AD23" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AD$13:AD$18=1)*($G$4:$G$9))</f>
+        <f aca="false">SUMPRODUCT((G$4:G$9=1)*(AD$13:AD$18=1))</f>
         <v>3</v>
       </c>
-      <c r="AE23" s="32" t="n">
-        <f aca="false">SUMPRODUCT((AE$13:AE$18=1)*($G$4:$G$9))</f>
-        <v>2</v>
-      </c>
+      <c r="AE23" s="32"/>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="40"/>
@@ -2022,109 +2016,106 @@
         <v>4</v>
       </c>
       <c r="F24" s="42" t="n">
-        <f aca="false">SUMPRODUCT((F$13:F$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(F$13:F$18=1))</f>
         <v>1</v>
       </c>
       <c r="G24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((G$13:G$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(G$13:G$18=1))</f>
         <v>1</v>
       </c>
       <c r="H24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((H$13:H$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(H$13:H$18=1))</f>
         <v>2</v>
       </c>
       <c r="I24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((I$13:I$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(I$13:I$18=1))</f>
         <v>2</v>
       </c>
       <c r="J24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((J$13:J$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(J$13:J$18=1))</f>
         <v>2</v>
       </c>
       <c r="K24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((K$13:K$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(K$13:K$18=1))</f>
         <v>2</v>
       </c>
       <c r="L24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((L$13:L$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(L$13:L$18=1))</f>
         <v>2</v>
       </c>
       <c r="M24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((M$13:M$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(M$13:M$18=1))</f>
         <v>2</v>
       </c>
       <c r="N24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((N$13:N$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(N$13:N$18=1))</f>
         <v>2</v>
       </c>
       <c r="O24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((O$13:O$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(O$13:O$18=1))</f>
         <v>2</v>
       </c>
       <c r="P24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((P$13:P$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(P$13:P$18=1))</f>
         <v>2</v>
       </c>
       <c r="Q24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Q$13:Q$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(Q$13:Q$18=1))</f>
         <v>2</v>
       </c>
       <c r="R24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((R$13:R$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(R$13:R$18=1))</f>
         <v>2</v>
       </c>
       <c r="S24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((S$13:S$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(S$13:S$18=1))</f>
         <v>2</v>
       </c>
       <c r="T24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((T$13:T$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(T$13:T$18=1))</f>
         <v>2</v>
       </c>
       <c r="U24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((U$13:U$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(U$13:U$18=1))</f>
         <v>2</v>
       </c>
       <c r="V24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((V$13:V$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(V$13:V$18=1))</f>
         <v>2</v>
       </c>
       <c r="W24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((W$13:W$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(W$13:W$18=1))</f>
         <v>2</v>
       </c>
       <c r="X24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((X$13:X$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(X$13:X$18=1))</f>
         <v>2</v>
       </c>
       <c r="Y24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Y$13:Y$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(Y$13:Y$18=1))</f>
         <v>1</v>
       </c>
       <c r="Z24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Z$13:Z$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(Z$13:Z$18=1))</f>
         <v>1</v>
       </c>
       <c r="AA24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AA$13:AA$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(AA$13:AA$18=1))</f>
         <v>0</v>
       </c>
       <c r="AB24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AB$13:AB$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(AB$13:AB$18=1))</f>
         <v>0</v>
       </c>
       <c r="AC24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AC$13:AC$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(AC$13:AC$18=1))</f>
         <v>0</v>
       </c>
       <c r="AD24" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AD$13:AD$18=1)*($H$4:$H$9))</f>
+        <f aca="false">SUMPRODUCT((H$4:H$9=1)*(AD$13:AD$18=1))</f>
         <v>0</v>
       </c>
-      <c r="AE24" s="32" t="n">
-        <f aca="false">SUMPRODUCT((AE$13:AE$18=1)*($H$4:$H$9))</f>
-        <v>0</v>
-      </c>
+      <c r="AE24" s="32"/>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="40"/>
@@ -2134,109 +2125,106 @@
         <v>5</v>
       </c>
       <c r="F25" s="42" t="n">
-        <f aca="false">SUMPRODUCT((F$13:F$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(F$13:F$18=1))</f>
         <v>1</v>
       </c>
       <c r="G25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((G$13:G$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(G$13:G$18=1))</f>
         <v>1</v>
       </c>
       <c r="H25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((H$13:H$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(H$13:H$18=1))</f>
         <v>2</v>
       </c>
       <c r="I25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((I$13:I$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(I$13:I$18=1))</f>
         <v>2</v>
       </c>
       <c r="J25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((J$13:J$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(J$13:J$18=1))</f>
         <v>2</v>
       </c>
       <c r="K25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((K$13:K$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(K$13:K$18=1))</f>
         <v>2</v>
       </c>
       <c r="L25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((L$13:L$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(L$13:L$18=1))</f>
         <v>2</v>
       </c>
       <c r="M25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((M$13:M$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(M$13:M$18=1))</f>
         <v>2</v>
       </c>
       <c r="N25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((N$13:N$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(N$13:N$18=1))</f>
         <v>2</v>
       </c>
       <c r="O25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((O$13:O$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(O$13:O$18=1))</f>
         <v>2</v>
       </c>
       <c r="P25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((P$13:P$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(P$13:P$18=1))</f>
         <v>2</v>
       </c>
       <c r="Q25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Q$13:Q$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(Q$13:Q$18=1))</f>
         <v>2</v>
       </c>
       <c r="R25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((R$13:R$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(R$13:R$18=1))</f>
         <v>2</v>
       </c>
       <c r="S25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((S$13:S$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(S$13:S$18=1))</f>
         <v>2</v>
       </c>
       <c r="T25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((T$13:T$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(T$13:T$18=1))</f>
         <v>2</v>
       </c>
       <c r="U25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((U$13:U$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(U$13:U$18=1))</f>
         <v>2</v>
       </c>
       <c r="V25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((V$13:V$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(V$13:V$18=1))</f>
         <v>2</v>
       </c>
       <c r="W25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((W$13:W$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(W$13:W$18=1))</f>
         <v>2</v>
       </c>
       <c r="X25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((X$13:X$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(X$13:X$18=1))</f>
         <v>2</v>
       </c>
       <c r="Y25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Y$13:Y$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(Y$13:Y$18=1))</f>
         <v>1</v>
       </c>
       <c r="Z25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Z$13:Z$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(Z$13:Z$18=1))</f>
         <v>1</v>
       </c>
       <c r="AA25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AA$13:AA$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(AA$13:AA$18=1))</f>
         <v>0</v>
       </c>
       <c r="AB25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AB$13:AB$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(AB$13:AB$18=1))</f>
         <v>0</v>
       </c>
       <c r="AC25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AC$13:AC$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(AC$13:AC$18=1))</f>
         <v>0</v>
       </c>
       <c r="AD25" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AD$13:AD$18=1)*($I$4:$I$9))</f>
+        <f aca="false">SUMPRODUCT((I$4:I$9=1)*(AD$13:AD$18=1))</f>
         <v>0</v>
       </c>
-      <c r="AE25" s="32" t="n">
-        <f aca="false">SUMPRODUCT((AE$13:AE$18=1)*($I$4:$I$9))</f>
-        <v>0</v>
-      </c>
+      <c r="AE25" s="32"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="40"/>
@@ -2246,109 +2234,106 @@
         <v>6</v>
       </c>
       <c r="F26" s="42" t="n">
-        <f aca="false">SUMPRODUCT((F$13:F$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(F$13:F$18=1))</f>
         <v>1</v>
       </c>
       <c r="G26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((G$13:G$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(G$13:G$18=1))</f>
         <v>1</v>
       </c>
       <c r="H26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((H$13:H$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(H$13:H$18=1))</f>
         <v>2</v>
       </c>
       <c r="I26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((I$13:I$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(I$13:I$18=1))</f>
         <v>2</v>
       </c>
       <c r="J26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((J$13:J$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(J$13:J$18=1))</f>
         <v>2</v>
       </c>
       <c r="K26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((K$13:K$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(K$13:K$18=1))</f>
         <v>2</v>
       </c>
       <c r="L26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((L$13:L$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(L$13:L$18=1))</f>
         <v>2</v>
       </c>
       <c r="M26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((M$13:M$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(M$13:M$18=1))</f>
         <v>2</v>
       </c>
       <c r="N26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((N$13:N$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(N$13:N$18=1))</f>
         <v>2</v>
       </c>
       <c r="O26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((O$13:O$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(O$13:O$18=1))</f>
         <v>2</v>
       </c>
       <c r="P26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((P$13:P$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(P$13:P$18=1))</f>
         <v>2</v>
       </c>
       <c r="Q26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Q$13:Q$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(Q$13:Q$18=1))</f>
         <v>2</v>
       </c>
       <c r="R26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((R$13:R$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(R$13:R$18=1))</f>
         <v>2</v>
       </c>
       <c r="S26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((S$13:S$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(S$13:S$18=1))</f>
         <v>2</v>
       </c>
       <c r="T26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((T$13:T$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(T$13:T$18=1))</f>
         <v>2</v>
       </c>
       <c r="U26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((U$13:U$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(U$13:U$18=1))</f>
         <v>2</v>
       </c>
       <c r="V26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((V$13:V$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(V$13:V$18=1))</f>
         <v>2</v>
       </c>
       <c r="W26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((W$13:W$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(W$13:W$18=1))</f>
         <v>2</v>
       </c>
       <c r="X26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((X$13:X$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(X$13:X$18=1))</f>
         <v>2</v>
       </c>
       <c r="Y26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Y$13:Y$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(Y$13:Y$18=1))</f>
         <v>1</v>
       </c>
       <c r="Z26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Z$13:Z$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(Z$13:Z$18=1))</f>
         <v>1</v>
       </c>
       <c r="AA26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AA$13:AA$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(AA$13:AA$18=1))</f>
         <v>0</v>
       </c>
       <c r="AB26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AB$13:AB$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(AB$13:AB$18=1))</f>
         <v>0</v>
       </c>
       <c r="AC26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AC$13:AC$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(AC$13:AC$18=1))</f>
         <v>0</v>
       </c>
       <c r="AD26" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AD$13:AD$18=1)*($J$4:$J$9))</f>
+        <f aca="false">SUMPRODUCT((J$4:J$9=1)*(AD$13:AD$18=1))</f>
         <v>0</v>
       </c>
-      <c r="AE26" s="32" t="n">
-        <f aca="false">SUMPRODUCT((AE$13:AE$18=1)*($J$4:$J$9))</f>
-        <v>0</v>
-      </c>
+      <c r="AE26" s="32"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="40"/>
@@ -2358,327 +2343,318 @@
         <v>7</v>
       </c>
       <c r="F27" s="42" t="n">
-        <f aca="false">SUMPRODUCT((F$13:F$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(F$13:F$18=1))</f>
         <v>1</v>
       </c>
       <c r="G27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((G$13:G$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(G$13:G$18=1))</f>
         <v>1</v>
       </c>
       <c r="H27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((H$13:H$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(H$13:H$18=1))</f>
         <v>2</v>
       </c>
       <c r="I27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((I$13:I$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(I$13:I$18=1))</f>
         <v>2</v>
       </c>
       <c r="J27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((J$13:J$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(J$13:J$18=1))</f>
         <v>2</v>
       </c>
       <c r="K27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((K$13:K$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(K$13:K$18=1))</f>
         <v>2</v>
       </c>
       <c r="L27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((L$13:L$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(L$13:L$18=1))</f>
         <v>2</v>
       </c>
       <c r="M27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((M$13:M$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(M$13:M$18=1))</f>
         <v>2</v>
       </c>
       <c r="N27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((N$13:N$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(N$13:N$18=1))</f>
         <v>2</v>
       </c>
       <c r="O27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((O$13:O$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(O$13:O$18=1))</f>
         <v>2</v>
       </c>
       <c r="P27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((P$13:P$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(P$13:P$18=1))</f>
         <v>2</v>
       </c>
       <c r="Q27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Q$13:Q$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(Q$13:Q$18=1))</f>
         <v>2</v>
       </c>
       <c r="R27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((R$13:R$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(R$13:R$18=1))</f>
         <v>2</v>
       </c>
       <c r="S27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((S$13:S$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(S$13:S$18=1))</f>
         <v>2</v>
       </c>
       <c r="T27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((T$13:T$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(T$13:T$18=1))</f>
         <v>2</v>
       </c>
       <c r="U27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((U$13:U$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(U$13:U$18=1))</f>
         <v>2</v>
       </c>
       <c r="V27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((V$13:V$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(V$13:V$18=1))</f>
         <v>2</v>
       </c>
       <c r="W27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((W$13:W$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(W$13:W$18=1))</f>
         <v>2</v>
       </c>
       <c r="X27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((X$13:X$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(X$13:X$18=1))</f>
         <v>2</v>
       </c>
       <c r="Y27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Y$13:Y$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(Y$13:Y$18=1))</f>
         <v>1</v>
       </c>
       <c r="Z27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Z$13:Z$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(Z$13:Z$18=1))</f>
         <v>1</v>
       </c>
       <c r="AA27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AA$13:AA$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(AA$13:AA$18=1))</f>
         <v>0</v>
       </c>
       <c r="AB27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AB$13:AB$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(AB$13:AB$18=1))</f>
         <v>0</v>
       </c>
       <c r="AC27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AC$13:AC$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(AC$13:AC$18=1))</f>
         <v>0</v>
       </c>
       <c r="AD27" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AD$13:AD$18=1)*($K$4:$K$9))</f>
+        <f aca="false">SUMPRODUCT((K$4:K$9=1)*(AD$13:AD$18=1))</f>
         <v>0</v>
       </c>
-      <c r="AE27" s="32" t="n">
-        <f aca="false">SUMPRODUCT((AE$13:AE$18=1)*($K$4:$K$9))</f>
-        <v>0</v>
-      </c>
+      <c r="AE27" s="32"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E28" s="41" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="42" t="n">
-        <f aca="false">SUMPRODUCT((F$13:F$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(F$13:F$18=1))</f>
         <v>1</v>
       </c>
       <c r="G28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((G$13:G$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(G$13:G$18=1))</f>
         <v>1</v>
       </c>
       <c r="H28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((H$13:H$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(H$13:H$18=1))</f>
         <v>1</v>
       </c>
       <c r="I28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((I$13:I$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(I$13:I$18=1))</f>
         <v>1</v>
       </c>
       <c r="J28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((J$13:J$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(J$13:J$18=1))</f>
         <v>1</v>
       </c>
       <c r="K28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((K$13:K$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(K$13:K$18=1))</f>
         <v>1</v>
       </c>
       <c r="L28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((L$13:L$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(L$13:L$18=1))</f>
         <v>1</v>
       </c>
       <c r="M28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((M$13:M$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(M$13:M$18=1))</f>
         <v>1</v>
       </c>
       <c r="N28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((N$13:N$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(N$13:N$18=1))</f>
         <v>1</v>
       </c>
       <c r="O28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((O$13:O$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(O$13:O$18=1))</f>
         <v>1</v>
       </c>
       <c r="P28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((P$13:P$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(P$13:P$18=1))</f>
         <v>1</v>
       </c>
       <c r="Q28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Q$13:Q$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(Q$13:Q$18=1))</f>
         <v>1</v>
       </c>
       <c r="R28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((R$13:R$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(R$13:R$18=1))</f>
         <v>1</v>
       </c>
       <c r="S28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((S$13:S$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(S$13:S$18=1))</f>
         <v>1</v>
       </c>
       <c r="T28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((T$13:T$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(T$13:T$18=1))</f>
         <v>1</v>
       </c>
       <c r="U28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((U$13:U$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(U$13:U$18=1))</f>
         <v>1</v>
       </c>
       <c r="V28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((V$13:V$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(V$13:V$18=1))</f>
         <v>1</v>
       </c>
       <c r="W28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((W$13:W$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(W$13:W$18=1))</f>
         <v>1</v>
       </c>
       <c r="X28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((X$13:X$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(X$13:X$18=1))</f>
         <v>1</v>
       </c>
       <c r="Y28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Y$13:Y$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(Y$13:Y$18=1))</f>
         <v>0</v>
       </c>
       <c r="Z28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((Z$13:Z$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(Z$13:Z$18=1))</f>
         <v>0</v>
       </c>
       <c r="AA28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AA$13:AA$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(AA$13:AA$18=1))</f>
         <v>0</v>
       </c>
       <c r="AB28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AB$13:AB$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(AB$13:AB$18=1))</f>
         <v>0</v>
       </c>
       <c r="AC28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AC$13:AC$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(AC$13:AC$18=1))</f>
         <v>0</v>
       </c>
       <c r="AD28" s="31" t="n">
-        <f aca="false">SUMPRODUCT((AD$13:AD$18=1)*($L$4:$L$9))</f>
+        <f aca="false">SUMPRODUCT((L$4:L$9=1)*(AD$13:AD$18=1))</f>
         <v>0</v>
       </c>
-      <c r="AE28" s="32" t="n">
-        <f aca="false">SUMPRODUCT((AE$13:AE$18=1)*($L$4:$L$9))</f>
-        <v>0</v>
-      </c>
+      <c r="AE28" s="32"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E29" s="43" t="s">
         <v>9</v>
       </c>
       <c r="F29" s="44" t="n">
-        <f aca="false">SUMPRODUCT((F$13:F$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(F$13:F$18=1))</f>
         <v>1</v>
       </c>
       <c r="G29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((G$13:G$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(G$13:G$18=1))</f>
         <v>1</v>
       </c>
       <c r="H29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((H$13:H$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(H$13:H$18=1))</f>
         <v>2</v>
       </c>
       <c r="I29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((I$13:I$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(I$13:I$18=1))</f>
         <v>2</v>
       </c>
       <c r="J29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((J$13:J$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(J$13:J$18=1))</f>
         <v>3</v>
       </c>
       <c r="K29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((K$13:K$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(K$13:K$18=1))</f>
         <v>3</v>
       </c>
       <c r="L29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((L$13:L$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(L$13:L$18=1))</f>
         <v>4</v>
       </c>
       <c r="M29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((M$13:M$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(M$13:M$18=1))</f>
         <v>6</v>
       </c>
       <c r="N29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((N$13:N$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(N$13:N$18=1))</f>
         <v>6</v>
       </c>
       <c r="O29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((O$13:O$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(O$13:O$18=1))</f>
         <v>6</v>
       </c>
       <c r="P29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((P$13:P$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(P$13:P$18=1))</f>
         <v>6</v>
       </c>
       <c r="Q29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((Q$13:Q$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(Q$13:Q$18=1))</f>
         <v>6</v>
       </c>
       <c r="R29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((R$13:R$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(R$13:R$18=1))</f>
         <v>6</v>
       </c>
       <c r="S29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((S$13:S$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(S$13:S$18=1))</f>
         <v>6</v>
       </c>
       <c r="T29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((T$13:T$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(T$13:T$18=1))</f>
         <v>6</v>
       </c>
       <c r="U29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((U$13:U$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(U$13:U$18=1))</f>
         <v>6</v>
       </c>
       <c r="V29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((V$13:V$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(V$13:V$18=1))</f>
         <v>6</v>
       </c>
       <c r="W29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((W$13:W$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(W$13:W$18=1))</f>
         <v>6</v>
       </c>
       <c r="X29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((X$13:X$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(X$13:X$18=1))</f>
         <v>6</v>
       </c>
       <c r="Y29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((Y$13:Y$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(Y$13:Y$18=1))</f>
         <v>5</v>
       </c>
       <c r="Z29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((Z$13:Z$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(Z$13:Z$18=1))</f>
         <v>5</v>
       </c>
       <c r="AA29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((AA$13:AA$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(AA$13:AA$18=1))</f>
         <v>4</v>
       </c>
       <c r="AB29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((AB$13:AB$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(AB$13:AB$18=1))</f>
         <v>4</v>
       </c>
       <c r="AC29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((AC$13:AC$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(AC$13:AC$18=1))</f>
         <v>3</v>
       </c>
       <c r="AD29" s="35" t="n">
-        <f aca="false">SUMPRODUCT((AD$13:AD$18=1)*($M$4:$M$9))</f>
+        <f aca="false">SUMPRODUCT((M$4:M$9=1)*(AD$13:AD$18=1))</f>
         <v>3</v>
       </c>
-      <c r="AE29" s="36" t="n">
-        <f aca="false">SUMPRODUCT((AE$13:AE$18=1)*($M$4:$M$9))</f>
-        <v>2</v>
-      </c>
+      <c r="AE29" s="36"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="45" t="s">
